--- a/91/merge/91/merge/StreamingAssets/Dialog.xlsx
+++ b/91/merge/91/merge/StreamingAssets/Dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonem\Documents\GitHub\void-red\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355DD222-0A07-457F-B459-063640830EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E940B806-4F6E-48D0-9872-A752B00E7FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>GetItem</t>
-  </si>
-  <si>
-    <t>Alv/1-2,ぬいぐるみ,よくできたぬいぐるみだ</t>
   </si>
   <si>
     <t>(エレベーターの音)</t>
@@ -390,6 +387,42 @@
   <si>
     <t>ああああ</t>
   </si>
+  <si>
+    <r>
+      <t>doll,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ぬいぐるみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よくできたぬいぐるみだ</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -417,6 +450,20 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -454,11 +501,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -716,19 +764,19 @@
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="G2" s="2"/>
       <c r="I2" s="2"/>
@@ -740,13 +788,13 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3"/>
@@ -766,8 +814,8 @@
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
+      <c r="D4" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -780,10 +828,10 @@
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
@@ -798,10 +846,10 @@
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
@@ -816,10 +864,10 @@
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
@@ -834,10 +882,10 @@
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
@@ -852,13 +900,13 @@
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2"/>
       <c r="G9" s="2"/>
@@ -871,10 +919,10 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2"/>
       <c r="E10" s="2"/>
@@ -888,16 +936,16 @@
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E11" s="2"/>
       <c r="G11" s="2"/>
@@ -910,16 +958,16 @@
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2"/>
       <c r="G12" s="2"/>
@@ -932,16 +980,16 @@
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2"/>
       <c r="G13" s="2"/>
@@ -954,16 +1002,16 @@
     </row>
     <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2"/>
       <c r="G14" s="2"/>
@@ -976,16 +1024,16 @@
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2"/>
       <c r="G15" s="2"/>
@@ -998,16 +1046,16 @@
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2"/>
       <c r="G16" s="2"/>
@@ -1020,16 +1068,16 @@
     </row>
     <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -1042,16 +1090,16 @@
     </row>
     <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2"/>
       <c r="G18" s="2"/>
@@ -1064,16 +1112,16 @@
     </row>
     <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2"/>
       <c r="G19" s="2"/>
@@ -1086,16 +1134,16 @@
     </row>
     <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2"/>
       <c r="G20" s="2"/>
@@ -1108,16 +1156,16 @@
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2"/>
       <c r="G21" s="2"/>
@@ -1130,16 +1178,16 @@
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2"/>
       <c r="G22" s="2"/>
@@ -1152,16 +1200,16 @@
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2"/>
       <c r="G23" s="2"/>
@@ -1174,16 +1222,16 @@
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2"/>
       <c r="G24" s="2"/>
@@ -1196,16 +1244,16 @@
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="2"/>
@@ -1218,16 +1266,16 @@
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2"/>
       <c r="G26" s="2"/>
@@ -1240,16 +1288,16 @@
     </row>
     <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="2"/>
@@ -1262,16 +1310,16 @@
     </row>
     <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="2"/>
@@ -1284,16 +1332,16 @@
     </row>
     <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="2"/>
@@ -1306,16 +1354,16 @@
     </row>
     <row r="30" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="2"/>
@@ -1328,16 +1376,16 @@
     </row>
     <row r="31" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="2"/>
@@ -1350,16 +1398,16 @@
     </row>
     <row r="32" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="2"/>
@@ -1372,16 +1420,16 @@
     </row>
     <row r="33" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="2"/>
@@ -1394,16 +1442,16 @@
     </row>
     <row r="34" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2"/>
       <c r="G34" s="2"/>
@@ -1416,16 +1464,16 @@
     </row>
     <row r="35" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2"/>
       <c r="G35" s="2"/>
@@ -1438,16 +1486,16 @@
     </row>
     <row r="36" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2"/>
       <c r="G36" s="2"/>
@@ -1460,16 +1508,16 @@
     </row>
     <row r="37" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2"/>
       <c r="G37" s="2"/>
@@ -1482,16 +1530,16 @@
     </row>
     <row r="38" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2"/>
       <c r="G38" s="2"/>
@@ -1504,16 +1552,16 @@
     </row>
     <row r="39" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" s="2"/>
       <c r="G39" s="2"/>
@@ -1526,16 +1574,16 @@
     </row>
     <row r="40" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2"/>
       <c r="G40" s="2"/>
@@ -1548,16 +1596,16 @@
     </row>
     <row r="41" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E41" s="2"/>
       <c r="G41" s="2"/>
@@ -1570,16 +1618,16 @@
     </row>
     <row r="42" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" s="2"/>
       <c r="G42" s="2"/>
@@ -1592,16 +1640,16 @@
     </row>
     <row r="43" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" s="2"/>
       <c r="G43" s="2"/>
@@ -1614,16 +1662,16 @@
     </row>
     <row r="44" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="2"/>
@@ -1636,16 +1684,16 @@
     </row>
     <row r="45" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="2"/>
@@ -1658,16 +1706,16 @@
     </row>
     <row r="46" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="2"/>
@@ -1680,16 +1728,16 @@
     </row>
     <row r="47" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="2"/>
@@ -1702,16 +1750,16 @@
     </row>
     <row r="48" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="2"/>
@@ -1724,16 +1772,16 @@
     </row>
     <row r="49" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E49" s="2"/>
       <c r="G49" s="2"/>
@@ -1746,16 +1794,16 @@
     </row>
     <row r="50" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="G50" s="2"/>
@@ -1768,16 +1816,16 @@
     </row>
     <row r="51" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="2"/>
@@ -1790,16 +1838,16 @@
     </row>
     <row r="52" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" s="2"/>
       <c r="G52" s="2"/>
@@ -1812,16 +1860,16 @@
     </row>
     <row r="53" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E53" s="2"/>
       <c r="G53" s="2"/>
@@ -1834,16 +1882,16 @@
     </row>
     <row r="54" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2"/>
       <c r="G54" s="2"/>
@@ -1856,16 +1904,16 @@
     </row>
     <row r="55" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" s="2"/>
       <c r="G55" s="2"/>
@@ -1878,16 +1926,16 @@
     </row>
     <row r="56" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E56" s="2"/>
       <c r="G56" s="2"/>
@@ -1900,16 +1948,16 @@
     </row>
     <row r="57" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="2"/>
@@ -1922,16 +1970,16 @@
     </row>
     <row r="58" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" s="2"/>
       <c r="G58" s="2"/>
@@ -1944,16 +1992,16 @@
     </row>
     <row r="59" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" s="2"/>
       <c r="G59" s="2"/>
@@ -1966,16 +2014,16 @@
     </row>
     <row r="60" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E60" s="2"/>
       <c r="G60" s="2"/>
@@ -1988,16 +2036,16 @@
     </row>
     <row r="61" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" s="2"/>
       <c r="G61" s="2"/>
@@ -2010,16 +2058,16 @@
     </row>
     <row r="62" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E62" s="2"/>
       <c r="G62" s="2"/>
@@ -2032,22 +2080,22 @@
     </row>
     <row r="63" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G63" s="2"/>
       <c r="I63" s="2"/>
@@ -2059,16 +2107,16 @@
     </row>
     <row r="64" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64" s="2"/>
       <c r="G64" s="2"/>
@@ -2081,16 +2129,16 @@
     </row>
     <row r="65" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="2"/>
       <c r="G65" s="2"/>
@@ -2103,16 +2151,16 @@
     </row>
     <row r="66" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E66" s="2"/>
       <c r="G66" s="2"/>
@@ -2125,16 +2173,16 @@
     </row>
     <row r="67" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="2"/>
@@ -2147,16 +2195,16 @@
     </row>
     <row r="68" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E68" s="2"/>
       <c r="G68" s="2"/>
@@ -2169,16 +2217,16 @@
     </row>
     <row r="69" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" s="2"/>
       <c r="G69" s="2"/>
@@ -2191,16 +2239,16 @@
     </row>
     <row r="70" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E70" s="2"/>
       <c r="G70" s="2"/>
@@ -2213,16 +2261,16 @@
     </row>
     <row r="71" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="2"/>
@@ -2235,7 +2283,7 @@
     </row>
     <row r="72" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C72" s="2"/>
       <c r="E72" s="2"/>
@@ -12520,10 +12568,10 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="2"/>
@@ -23569,16 +23617,16 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
@@ -23592,10 +23640,10 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
@@ -23610,10 +23658,10 @@
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
@@ -34640,28 +34688,28 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3">
         <v>45658</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" s="2"/>
       <c r="K2" s="2"/>
@@ -34672,13 +34720,13 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
@@ -34694,16 +34742,16 @@
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="2"/>
@@ -34716,13 +34764,13 @@
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -34738,16 +34786,16 @@
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2"/>
       <c r="G6" s="2"/>
@@ -34760,16 +34808,16 @@
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2"/>
       <c r="G7" s="2"/>
@@ -34782,10 +34830,10 @@
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
